--- a/student_assessment_forms/006_statics_equilibrium_forces_quiz--student_assessment_forms.xlsx
+++ b/student_assessment_forms/006_statics_equilibrium_forces_quiz--student_assessment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -707,7 +707,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C45"/>
+  <dimension ref="A1:C42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>f_=_m1_a1_+_m2_a2</t>
+          <t>f_=_m1_a</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>f = m1 a1 + m2 a2</t>
+          <t>F = m1 a</t>
         </is>
       </c>
     </row>
@@ -859,12 +859,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>f_=_m1_a1_+_m2_a2</t>
+          <t>f_=_m1_a1_+_m2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>F = m1 a1 + m2 a2</t>
+          <t>f = m1 a1 + m2</t>
         </is>
       </c>
     </row>
@@ -876,12 +876,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>f_=_m1_a</t>
+          <t>f_=_m1_a2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>F = m1 a</t>
+          <t>f = m1 a2</t>
         </is>
       </c>
     </row>
@@ -893,12 +893,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>f_=_m1_a1_+_m2</t>
+          <t>f_=_m1_+_m2_a</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>f = m1 a1 + m2</t>
+          <t>f = m1 + m2 a</t>
         </is>
       </c>
     </row>
@@ -910,12 +910,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>f_=_m1_a2</t>
+          <t>f_=_(m1)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>f = m1 a2</t>
+          <t>f = (m1)</t>
         </is>
       </c>
     </row>
@@ -927,12 +927,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>f_=_m1_a</t>
+          <t>f_=_m2_a1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>F = m1 a</t>
+          <t>F = m2 a1</t>
         </is>
       </c>
     </row>
@@ -944,12 +944,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>f_=_m1_+_m2_a</t>
+          <t>f_=_m2_a2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>f = m1 + m2 a</t>
+          <t>f = m2 a2</t>
         </is>
       </c>
     </row>
@@ -961,12 +961,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>f_=_(m1)</t>
+          <t>f_=_m2_a</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>f = (m1)</t>
+          <t>F = m2 a</t>
         </is>
       </c>
     </row>
@@ -978,63 +978,63 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>f_=_m2_a1</t>
+          <t>f_=_m1_+_m2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>F = m2 a1</t>
+          <t>f = m1 + m2</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>concept_1_choices</t>
+          <t>concept_2_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>f_=_m2_a2</t>
+          <t>f1_=_m1_a1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>f = m2 a2</t>
+          <t>F1 = m1 a1</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>concept_1_choices</t>
+          <t>concept_2_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>f_=_m2_a</t>
+          <t>f1_=_m1_a1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>F = m2 a</t>
+          <t>f1 = m1 a1</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>concept_1_choices</t>
+          <t>concept_2_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>f_=_m1_+_m2</t>
+          <t>f1_=_m1_a</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>f = m1 + m2</t>
+          <t>F1 = m1 a</t>
         </is>
       </c>
     </row>
@@ -1046,12 +1046,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>f1_=_m1_a1</t>
+          <t>f1_=_m1_a</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>F1 = m1 a1</t>
+          <t>f1 = m1 a</t>
         </is>
       </c>
     </row>
@@ -1063,12 +1063,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>f1_=_m1_a1</t>
+          <t>f1_=_(m1)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>f1 = m1 a1</t>
+          <t>F1 = (m1)</t>
         </is>
       </c>
     </row>
@@ -1080,12 +1080,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>f1_=_m1_a</t>
+          <t>f1_=_(m1)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>F1 = m1 a</t>
+          <t>f1 = (m1)</t>
         </is>
       </c>
     </row>
@@ -1097,12 +1097,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>f1_=_m1_a</t>
+          <t>f1_=_m1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>f1 = m1 a</t>
+          <t>F1 = m1</t>
         </is>
       </c>
     </row>
@@ -1114,12 +1114,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>f1_=_(m1)</t>
+          <t>f1_=_m1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>F1 = (m1)</t>
+          <t>f1 = m1</t>
         </is>
       </c>
     </row>
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>f1_=_(m1)</t>
+          <t>f1_=_m2_a1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>f1 = (m1)</t>
+          <t>F1 = m2 a1</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>f1_=_m1</t>
+          <t>f1_=_m2_a1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>F1 = m1</t>
+          <t>f1 = m2 a1</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>f1_=_m1</t>
+          <t>f1_=_m2_a</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>f1 = m1</t>
+          <t>F1 = m2 a</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>f1_=_m2_a1</t>
+          <t>f1_=_m2_a</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>F1 = m2 a1</t>
+          <t>f1 = m2 a</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>f1_=_m2_a1</t>
+          <t>f1_=_m2</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>f1 = m2 a1</t>
+          <t>F1 = m2</t>
         </is>
       </c>
     </row>
@@ -1216,63 +1216,63 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>f1_=_m2_a</t>
+          <t>f1_=_m2</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>F1 = m2 a</t>
+          <t>f1 = m2</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>concept_2_choices</t>
+          <t>concept_3_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>f1_=_m2_a</t>
+          <t>a1_=_m1_f1</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>f1 = m2 a</t>
+          <t>a1 = m1 F1</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>concept_2_choices</t>
+          <t>concept_3_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>f1_=_m2</t>
+          <t>a1_=_m1_f1</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>F1 = m2</t>
+          <t>a1 = m1 f1</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>concept_2_choices</t>
+          <t>concept_3_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>f1_=_m2</t>
+          <t>a1_=_m1_f</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>f1 = m2</t>
+          <t>a1 = m1 F</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>a1_=_m1_f1</t>
+          <t>a1_=_m1_f</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>a1 = m1 F1</t>
+          <t>a1 = m1 f</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>a1_=_m1_f1</t>
+          <t>f1_=_m1_a1</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>a1 = m1 f1</t>
+          <t>F1 = m1 a1</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>a1_=_m1_f</t>
+          <t>f1_=_m1_a1</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>a1 = m1 F</t>
+          <t>f1 = m1 a1</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>a1_=_m1_f</t>
+          <t>a1_=_m1</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>a1 = m1 f</t>
+          <t>a1 = m1</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>f1_=_m1_a1</t>
+          <t>f1_=_m1</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>F1 = m1 a1</t>
+          <t>F1 = m1</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>f1_=_m1_a1</t>
+          <t>a1_=_m1_a</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>f1 = m1 a1</t>
+          <t>a1 = m1 a</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>a1_=_m1</t>
+          <t>f1_=_m1_a</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>a1 = m1</t>
+          <t>F1 = m1 a</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>f1_=_m1</t>
+          <t>a1_=_m1_+_m2</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>F1 = m1</t>
+          <t>a1 = m1 + m2</t>
         </is>
       </c>
     </row>
@@ -1420,61 +1420,10 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>a1_=_m1_a</t>
+          <t>f1_=_m1_+_m2</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
-        <is>
-          <t>a1 = m1 a</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>concept_3_choices</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>f1_=_m1_a</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>F1 = m1 a</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>concept_3_choices</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>a1_=_m1_+_m2</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>a1 = m1 + m2</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>concept_3_choices</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>f1_=_m1_+_m2</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
         <is>
           <t>F1 = m1 + m2</t>
         </is>
